--- a/DATA/Aggregated data/International reserves/International reserves aggregated.xlsx
+++ b/DATA/Aggregated data/International reserves/International reserves aggregated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Desktop\Masterproef\DATA\Aggregated data\International reserves\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\GitHub\Masterthesis\DATA\Aggregated data\International reserves\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC07282-48F7-460C-86E2-F377D88CC570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6CF253-04BD-4D60-ABE6-ED2D9094217B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +632,7 @@
             <c:numRef>
               <c:f>'Base year'!$C$2:$C$130</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="129"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -1447,7 +1448,7 @@
             <c:numRef>
               <c:f>'Base year'!$D$2:$D$130</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="129"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -2263,7 +2264,7 @@
             <c:numRef>
               <c:f>'Base year'!$E$2:$E$130</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="129"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -3088,7 +3089,7 @@
             <c:numRef>
               <c:f>'Base year'!$F$2:$F$130</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="129"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -3563,7 +3564,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4541,11 +4542,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M131"/>
+  <dimension ref="B1:M132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4570,16 +4571,16 @@
       <c r="B2" s="1">
         <v>42005</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>111066762807.11499</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>80715986539.039993</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>155423010000</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>357380579707.56897</v>
       </c>
       <c r="J2" t="s">
@@ -4599,16 +4600,16 @@
       <c r="B3" s="1">
         <v>42036</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>112481794245.31999</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>80837009080.75</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>156935390000</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>357536838134.98297</v>
       </c>
       <c r="I3" t="s">
@@ -4635,16 +4636,16 @@
       <c r="B4" s="1">
         <v>42064</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>108570554534.939</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>80458507744.87001</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>156319190000</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>357928326530.85602</v>
       </c>
       <c r="I4" t="s">
@@ -4671,16 +4672,16 @@
       <c r="B5" s="1">
         <v>42095</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>107850462420.34401</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>80850116094.989975</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>161103290000</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>365124398042.30896</v>
       </c>
       <c r="I5" t="s">
@@ -4707,16 +4708,16 @@
       <c r="B6" s="1">
         <v>42125</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>107798024910.41701</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>80405038802.649994</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>158518370000</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>366699945281.67395</v>
       </c>
       <c r="I6" t="s">
@@ -4743,16 +4744,16 @@
       <c r="B7" s="1">
         <v>42156</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>105083991969.99001</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>80644259150.559998</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>160273970000</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>369951772871.64099</v>
       </c>
       <c r="I7" t="s">
@@ -4779,16 +4780,16 @@
       <c r="B8" s="1">
         <v>42186</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>104823969808.92601</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>80332384841.309982</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>156944030000</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>366014694912.13397</v>
       </c>
     </row>
@@ -4796,16 +4797,16 @@
       <c r="B9" s="1">
         <v>42217</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>102489013455.81999</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>80255433999.340012</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>155838100000</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>363114004631.18201</v>
       </c>
     </row>
@@ -4813,16 +4814,16 @@
       <c r="B10" s="1">
         <v>42248</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>98876149477.459503</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>80550511737.019989</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>155533430000</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>363301134503.078</v>
       </c>
     </row>
@@ -4830,16 +4831,16 @@
       <c r="B11" s="1">
         <v>42278</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>97836228870.934402</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>81097820536.360001</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>158293930000</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>364804750402.76904</v>
       </c>
     </row>
@@ -4847,16 +4848,16 @@
       <c r="B12" s="1">
         <v>42309</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>97583805480.086411</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>80173186103.62999</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>155680970000</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>363649910233.02802</v>
       </c>
     </row>
@@ -4864,16 +4865,16 @@
       <c r="B13" s="1">
         <v>42339</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>103268247088.71899</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>80666864742.149994</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>156513950000</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>363149330364.60699</v>
       </c>
     </row>
@@ -4881,16 +4882,16 @@
       <c r="B14" s="1">
         <v>42370</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>99334128541.035995</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>80692425965.22998</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>160114250000</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>362478384956.75</v>
       </c>
     </row>
@@ -4898,16 +4899,16 @@
       <c r="B15" s="1">
         <v>42401</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>101451511705.095</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>81877589659.589996</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>167971320000</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>360927719374.89398</v>
       </c>
     </row>
@@ -4915,16 +4916,16 @@
       <c r="B16" s="1">
         <v>42430</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>104443809676.73199</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>82977042142.819992</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>175073290000</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>365037706266.25305</v>
       </c>
     </row>
@@ -4932,16 +4933,16 @@
       <c r="B17" s="1">
         <v>42461</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>104565425935.041</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>83736272496.299988</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>178568340000</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>367683941438.01202</v>
       </c>
     </row>
@@ -4949,16 +4950,16 @@
       <c r="B18" s="1">
         <v>42491</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>100532832900.311</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>82927198872.300003</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>175477000000</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>366078772426.25098</v>
       </c>
     </row>
@@ -4966,16 +4967,16 @@
       <c r="B19" s="1">
         <v>42522</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>106477401169.09799</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>85284318324.630005</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>178668890000</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>365090265594.1391</v>
       </c>
     </row>
@@ -4983,16 +4984,16 @@
       <c r="B20" s="1">
         <v>42552</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>108046725822.547</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>85506227793.149994</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>180203660000</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>366584859890.26105</v>
       </c>
     </row>
@@ -5000,16 +5001,16 @@
       <c r="B21" s="1">
         <v>42583</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>110225937040.59201</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>85791979065.959991</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>180802640000</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>370646171456.987</v>
       </c>
     </row>
@@ -5017,16 +5018,16 @@
       <c r="B22" s="1">
         <v>42614</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>112357322021.306</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>86139109264.850006</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>180468740000</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>372953962922.867</v>
       </c>
     </row>
@@ -5034,16 +5035,16 @@
       <c r="B23" s="1">
         <v>42644</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>111845868944.362</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>85105775423.029999</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>180261170000</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>370364905019.091</v>
       </c>
     </row>
@@ -5051,16 +5052,16 @@
       <c r="B24" s="1">
         <v>42675</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>108490981418.797</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>81451073332.960007</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>174705250000</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>367182753205.92902</v>
       </c>
     </row>
@@ -5068,16 +5069,16 @@
       <c r="B25" s="1">
         <v>42705</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>113493392851.05901</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>80691786823.139984</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>171853240000</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>366307950374.06799</v>
       </c>
     </row>
@@ -5085,16 +5086,16 @@
       <c r="B26" s="1">
         <v>42736</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>113904589254.927</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>81376447559.930008</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>179161410000</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>369243250449.26099</v>
       </c>
     </row>
@@ -5102,16 +5103,16 @@
       <c r="B27" s="1">
         <v>42767</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>116709645394.04399</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>81436087948.470001</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>183002140000</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>369104366701.83514</v>
       </c>
     </row>
@@ -5119,16 +5120,16 @@
       <c r="B28" s="1">
         <v>42795</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>118665259946.974</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>80893788817.240005</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>180869190000</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>370483318925.31403</v>
       </c>
     </row>
@@ -5136,16 +5137,16 @@
       <c r="B29" s="1">
         <v>42826</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>120083391594.007</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>82015344440.569992</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>184469920000</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>371771287779.22699</v>
       </c>
     </row>
@@ -5153,16 +5154,16 @@
       <c r="B30" s="1">
         <v>42856</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>121739978059.681</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>82176526782.73999</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <v>184148100000</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <v>373660399012.96802</v>
       </c>
     </row>
@@ -5170,16 +5171,16 @@
       <c r="B31" s="1">
         <v>42887</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>119948958309.784</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>81321205967.110016</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <v>185555110000</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <v>375762066781.08887</v>
       </c>
     </row>
@@ -5187,16 +5188,16 @@
       <c r="B32" s="1">
         <v>42917</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>124484915073.133</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>81065255222.280014</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <v>190381340000</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <v>378938347686.47687</v>
       </c>
     </row>
@@ -5204,16 +5205,16 @@
       <c r="B33" s="1">
         <v>42948</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>125386969481.53999</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>81725381858.26001</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="2">
         <v>196914300000</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2">
         <v>379996464071.87701</v>
       </c>
     </row>
@@ -5221,16 +5222,16 @@
       <c r="B34" s="1">
         <v>42979</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>126079701487.381</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>80962231790.199997</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>199304480000</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>379854298772.67999</v>
       </c>
     </row>
@@ -5238,16 +5239,16 @@
       <c r="B35" s="1">
         <v>43009</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>123253081555.465</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>80419106421.789993</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <v>200525760000</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>379641737768.02301</v>
       </c>
     </row>
@@ -5255,16 +5256,16 @@
       <c r="B36" s="1">
         <v>43040</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>122638205003.64499</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>80309845151.23999</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <v>203073060000</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>382422052979.40601</v>
       </c>
     </row>
@@ -5272,16 +5273,16 @@
       <c r="B37" s="1">
         <v>43070</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>126857395382.957</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>81569899864.039993</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <v>202562310000</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>384453153318.38403</v>
       </c>
     </row>
@@ -5289,16 +5290,16 @@
       <c r="B38" s="1">
         <v>43101</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>128498172045.451</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>81223997479.490005</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="2">
         <v>214665120000</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <v>390908689745.138</v>
       </c>
     </row>
@@ -5306,16 +5307,16 @@
       <c r="B39" s="1">
         <v>43132</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>124612690442.41301</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>80431587789.539993</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <v>212734930000</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>389927687983.95398</v>
       </c>
     </row>
@@ -5323,16 +5324,16 @@
       <c r="B40" s="1">
         <v>43160</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>122543191256.54599</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>80511200839.660004</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>215614700000</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <v>391901710679.60297</v>
       </c>
     </row>
@@ -5340,16 +5341,16 @@
       <c r="B41" s="1">
         <v>43191</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <v>121437875918.491</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>79608786457.960007</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <v>215152080000</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <v>393570532808.16199</v>
       </c>
     </row>
@@ -5357,16 +5358,16 @@
       <c r="B42" s="1">
         <v>43221</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <v>119547940177.36501</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>79202376079.769989</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <v>212553370000</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2">
         <v>394138110741.716</v>
       </c>
     </row>
@@ -5374,16 +5375,16 @@
       <c r="B43" s="1">
         <v>43252</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <v>116681858859.88901</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>77525104966.170013</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="2">
         <v>206790710000</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <v>395418762282.26489</v>
       </c>
     </row>
@@ -5391,16 +5392,16 @@
       <c r="B44" s="1">
         <v>43282</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <v>115225049967.44901</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <v>76721649813.990005</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="2">
         <v>205506740000</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <v>397543453741.22491</v>
       </c>
     </row>
@@ -5408,16 +5409,16 @@
       <c r="B45" s="1">
         <v>43313</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
         <v>114902149265.56</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <v>77933935016.759995</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="2">
         <v>204535680000</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="2">
         <v>396217605517.33698</v>
       </c>
     </row>
@@ -5425,16 +5426,16 @@
       <c r="B46" s="1">
         <v>43344</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2">
         <v>111841286259.472</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <v>74938792810.819992</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="2">
         <v>204457060000</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="2">
         <v>398063841002.052</v>
       </c>
     </row>
@@ -5442,16 +5443,16 @@
       <c r="B47" s="1">
         <v>43374</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2">
         <v>112068703678.44601</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>74710905302.539993</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="2">
         <v>201784550000</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <v>397839321530.37402</v>
       </c>
     </row>
@@ -5459,16 +5460,16 @@
       <c r="B48" s="1">
         <v>43405</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2">
         <v>114115246222.633</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>75682148677.340012</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <v>203153030000</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <v>398078931095.20502</v>
       </c>
     </row>
@@ -5476,16 +5477,16 @@
       <c r="B49" s="1">
         <v>43435</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2">
         <v>117424645942.922</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <v>79193369769.110001</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="2">
         <v>205641070000</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <v>398780329741.70203</v>
       </c>
     </row>
@@ -5493,16 +5494,16 @@
       <c r="B50" s="1">
         <v>43466</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2">
         <v>116772193014.72099</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="2">
         <v>82487075349.369995</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="2">
         <v>209910750000</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="2">
         <v>400587058922.44299</v>
       </c>
     </row>
@@ -5510,16 +5511,16 @@
       <c r="B51" s="1">
         <v>43497</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="2">
         <v>119934012481.12701</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <v>82780833858.320007</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="2">
         <v>212540700000</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="2">
         <v>399735293869.65302</v>
       </c>
     </row>
@@ -5527,16 +5528,16 @@
       <c r="B52" s="1">
         <v>43525</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="2">
         <v>121269199866.062</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <v>83613235476.609985</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="2">
         <v>212183050000</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <v>400314754088.65509</v>
       </c>
     </row>
@@ -5544,16 +5545,16 @@
       <c r="B53" s="1">
         <v>43556</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2">
         <v>121039179247.117</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>83878770948.069992</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="2">
         <v>210500500000</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <v>398986284851.67102</v>
       </c>
     </row>
@@ -5561,16 +5562,16 @@
       <c r="B54" s="1">
         <v>43586</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="2">
         <v>117113609356.10101</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <v>85357459578.490005</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="2">
         <v>209955740000</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="2">
         <v>396919590170.5769</v>
       </c>
     </row>
@@ -5578,16 +5579,16 @@
       <c r="B55" s="1">
         <v>43617</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="2">
         <v>120281951799.33699</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <v>84931550011.680008</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="2">
         <v>215808410000</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>398016397672.50806</v>
       </c>
     </row>
@@ -5595,16 +5596,16 @@
       <c r="B56" s="1">
         <v>43647</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="2">
         <v>122299287090.66199</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <v>85175756150.550003</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="2">
         <v>218365890000</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <v>398052050776.539</v>
       </c>
     </row>
@@ -5612,16 +5613,16 @@
       <c r="B57" s="1">
         <v>43678</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="2">
         <v>122549482205.51601</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <v>86031003714.330017</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="2">
         <v>220169710000</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="2">
         <v>396414219032.88885</v>
       </c>
     </row>
@@ -5629,16 +5630,16 @@
       <c r="B58" s="1">
         <v>43709</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="2">
         <v>120568337001.92101</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>85581756988.349991</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="2">
         <v>220530700000</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="2">
         <v>398253889163.02002</v>
       </c>
     </row>
@@ -5646,16 +5647,16 @@
       <c r="B59" s="1">
         <v>43739</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="2">
         <v>122915409932.134</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <v>85834057551.649994</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="2">
         <v>222782740000</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <v>401283366663.62488</v>
       </c>
     </row>
@@ -5663,16 +5664,16 @@
       <c r="B60" s="1">
         <v>43770</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="2">
         <v>122953919050.63901</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <v>86227577920.259995</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="2">
         <v>221036360000</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <v>402393948117.7951</v>
       </c>
     </row>
@@ -5680,16 +5681,16 @@
       <c r="B61" s="1">
         <v>43800</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="2">
         <v>125339390220.65799</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>87839536214.619995</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="2">
         <v>224326660000</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="2">
         <v>403704746313.85596</v>
       </c>
     </row>
@@ -5697,16 +5698,16 @@
       <c r="B62" s="1">
         <v>43831</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="2">
         <v>127735559801.69099</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <v>86868552410.580002</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="2">
         <v>230309480000</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>404547090736.6991</v>
       </c>
     </row>
@@ -5714,16 +5715,16 @@
       <c r="B63" s="1">
         <v>43862</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="2">
         <v>126302309068.569</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <v>88186973478.509995</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="2">
         <v>229456050000</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="2">
         <v>404034790326.16888</v>
       </c>
     </row>
@@ -5731,16 +5732,16 @@
       <c r="B64" s="1">
         <v>43891</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="2">
         <v>116874655629.18399</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="2">
         <v>88861497258.949997</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="2">
         <v>226468690000</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="2">
         <v>395038306474.02698</v>
       </c>
     </row>
@@ -5748,16 +5749,16 @@
       <c r="B65" s="1">
         <v>43922</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="2">
         <v>123563205770.056</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="2">
         <v>90942706953.249985</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="2">
         <v>235708910000</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="2">
         <v>398510801886.00397</v>
       </c>
     </row>
@@ -5765,16 +5766,16 @@
       <c r="B66" s="1">
         <v>43952</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="2">
         <v>126211125225.306</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="2">
         <v>93288103109.389969</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="2">
         <v>237245780000</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="2">
         <v>401410904952.52106</v>
       </c>
     </row>
@@ -5782,16 +5783,16 @@
       <c r="B67" s="1">
         <v>43983</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="2">
         <v>127236011911.942</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="2">
         <v>93469870078.449982</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="2">
         <v>241583010000</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="2">
         <v>404799148766.20697</v>
       </c>
     </row>
@@ -5799,16 +5800,16 @@
       <c r="B68" s="1">
         <v>44013</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="2">
         <v>130128478816.132</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <v>98600522044.009995</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="2">
         <v>250355510000</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="2">
         <v>410593404726.42999</v>
       </c>
     </row>
@@ -5816,16 +5817,16 @@
       <c r="B69" s="1">
         <v>44044</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="2">
         <v>132062022946.72699</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <v>98954894274.73999</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="2">
         <v>254518260000</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="2">
         <v>412984446395.4649</v>
       </c>
     </row>
@@ -5833,16 +5834,16 @@
       <c r="B70" s="1">
         <v>44075</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="2">
         <v>130366649306.43199</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <v>100443319322.19</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="2">
         <v>251053110000</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="2">
         <v>414590606559.83197</v>
       </c>
     </row>
@@ -5850,16 +5851,16 @@
       <c r="B71" s="1">
         <v>44105</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="2">
         <v>128828355301.83701</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <v>103802617359.46001</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="2">
         <v>248511400000</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="2">
         <v>420544831611.97998</v>
       </c>
     </row>
@@ -5867,16 +5868,16 @@
       <c r="B72" s="1">
         <v>44136</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="2">
         <v>129065397378.067</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <v>104815436334.57999</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="2">
         <v>253493750000</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="2">
         <v>430424542355.078</v>
       </c>
     </row>
@@ -5884,16 +5885,16 @@
       <c r="B73" s="1">
         <v>44166</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="2">
         <v>131139029065.84201</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>110117434184.97998</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="2">
         <v>258134370000</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="2">
         <v>437112592614.3031</v>
       </c>
     </row>
@@ -5901,16 +5902,16 @@
       <c r="B74" s="1">
         <v>44197</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="2">
         <v>133352532466.451</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="2">
         <v>108673807555.73</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="2">
         <v>256838630000</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="2">
         <v>436754160058.38098</v>
       </c>
     </row>
@@ -5918,16 +5919,16 @@
       <c r="B75" s="1">
         <v>44228</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="2">
         <v>134292886347.81999</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="2">
         <v>105161198195.04001</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="2">
         <v>253916370000</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="2">
         <v>441529921314.45801</v>
       </c>
     </row>
@@ -5935,16 +5936,16 @@
       <c r="B76" s="1">
         <v>44256</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="2">
         <v>132849600065.702</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>104483778782.73003</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="2">
         <v>245535070000</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="2">
         <v>440162891828.43597</v>
       </c>
     </row>
@@ -5952,16 +5953,16 @@
       <c r="B77" s="1">
         <v>44287</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="2">
         <v>134332574265.959</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <v>107705106907.05003</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="2">
         <v>250372000000</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="2">
         <v>446318028736.33099</v>
       </c>
     </row>
@@ -5969,16 +5970,16 @@
       <c r="B78" s="1">
         <v>44317</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="2">
         <v>131585671517.507</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>107250703705.80005</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="2">
         <v>251784340000</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="2">
         <v>450469742514.16101</v>
       </c>
     </row>
@@ -5986,16 +5987,16 @@
       <c r="B79" s="1">
         <v>44348</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="2">
         <v>132654263680.00201</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="2">
         <v>105762716633.75002</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="2">
         <v>246528760000</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="2">
         <v>448131287767.52087</v>
       </c>
     </row>
@@ -6003,16 +6004,16 @@
       <c r="B80" s="1">
         <v>44378</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="2">
         <v>132723921939.52901</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="2">
         <v>107151465067.63002</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="2">
         <v>248018700000</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="2">
         <v>452713795151.00397</v>
       </c>
     </row>
@@ -6020,16 +6021,16 @@
       <c r="B81" s="1">
         <v>44409</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="2">
         <v>140209666477.97202</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="2">
         <v>107964673925.04002</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="2">
         <v>252012590000</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="2">
         <v>457985994959.15497</v>
       </c>
     </row>
@@ -6037,16 +6038,16 @@
       <c r="B82" s="1">
         <v>44440</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="2">
         <v>142462749479.28098</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>106596231376.35004</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="2">
         <v>244670550000</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="2">
         <v>457948887899.48499</v>
       </c>
     </row>
@@ -6054,16 +6055,16 @@
       <c r="B83" s="1">
         <v>44470</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="2">
         <v>140945772293.42499</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="2">
         <v>107888866504.90004</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="2">
         <v>246099830000</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="2">
         <v>463271289450.867</v>
       </c>
     </row>
@@ -6071,16 +6072,16 @@
       <c r="B84" s="1">
         <v>44501</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="2">
         <v>141346541826.35699</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="2">
         <v>107723636414.81004</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="2">
         <v>243016650000</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="2">
         <v>457996289518.34998</v>
       </c>
     </row>
@@ -6088,16 +6089,16 @@
       <c r="B85" s="1">
         <v>44531</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <v>140310235087.496</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <v>108794414703.29001</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="2">
         <v>245996760000</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="2">
         <v>457169379936.91199</v>
       </c>
     </row>
@@ -6105,16 +6106,16 @@
       <c r="B86" s="1">
         <v>44562</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <v>136827585041.983</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <v>107688567583.8</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="2">
         <v>242772440000</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="2">
         <v>455583882483.44299</v>
       </c>
     </row>
@@ -6122,16 +6123,16 @@
       <c r="B87" s="1">
         <v>44593</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="2">
         <v>136604347891.91501</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <v>107801188531.36</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="2">
         <v>245052680000</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="2">
         <v>455833577101.4231</v>
       </c>
     </row>
@@ -6139,16 +6140,16 @@
       <c r="B88" s="1">
         <v>44621</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="2">
         <v>134259232249.44002</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <v>107308909453.37997</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="2">
         <v>242430460000</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="2">
         <v>451865372152.25702</v>
       </c>
     </row>
@@ -6156,16 +6157,16 @@
       <c r="B89" s="1">
         <v>44652</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="2">
         <v>130864367641.017</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="2">
         <v>105400454395.65996</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="2">
         <v>228574510000</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="2">
         <v>443460756419.96002</v>
       </c>
     </row>
@@ -6173,16 +6174,16 @@
       <c r="B90" s="1">
         <v>44682</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="2">
         <v>130872699987.65001</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <v>103646889350.31996</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="2">
         <v>229997870000</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="2">
         <v>441813330245.52399</v>
       </c>
     </row>
@@ -6190,16 +6191,16 @@
       <c r="B91" s="1">
         <v>44713</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="2">
         <v>131759279310.98801</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <v>100853668468.53001</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="2">
         <v>222292500000</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="2">
         <v>432319726104.19403</v>
       </c>
     </row>
@@ -6207,16 +6208,16 @@
       <c r="B92" s="1">
         <v>44743</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <v>127754186814.416</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <v>99838579682.670029</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="2">
         <v>220019140000</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <v>432821210106.4071</v>
       </c>
     </row>
@@ -6224,16 +6225,16 @@
       <c r="B93" s="1">
         <v>44774</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <v>127836546540.974</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>97441854367.620041</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="2">
         <v>215020440000</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="2">
         <v>430529645983.36896</v>
       </c>
     </row>
@@ -6241,16 +6242,16 @@
       <c r="B94" s="1">
         <v>44805</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="2">
         <v>126579037839.44701</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="2">
         <v>93000009939.77005</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="2">
         <v>199444550000</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="2">
         <v>410980207678.97894</v>
       </c>
     </row>
@@ -6258,16 +6259,16 @@
       <c r="B95" s="1">
         <v>44835</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="2">
         <v>126038262186.347</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="2">
         <v>94027865683.630051</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="2">
         <v>201906850000</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="2">
         <v>408128703886.961</v>
       </c>
     </row>
@@ -6275,16 +6276,16 @@
       <c r="B96" s="1">
         <v>44866</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="2">
         <v>129563558393.685</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="2">
         <v>95123189758.210037</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="2">
         <v>210696530000</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="2">
         <v>410240310006.33801</v>
       </c>
     </row>
@@ -6292,16 +6293,16 @@
       <c r="B97" s="1">
         <v>44896</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="2">
         <v>132644357980.272</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="2">
         <v>96149171235.700012</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="2">
         <v>216632540000</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="2">
         <v>417280090434.54999</v>
       </c>
     </row>
@@ -6309,16 +6310,16 @@
       <c r="B98" s="1">
         <v>44927</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="2">
         <v>134547228593.46599</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="2">
         <v>100665502296.8</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="2">
         <v>225486900000</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="2">
         <v>424026485089.323</v>
       </c>
     </row>
@@ -6326,16 +6327,16 @@
       <c r="B99" s="1">
         <v>44958</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="2">
         <v>135754814227.411</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="2">
         <v>98216138526.960007</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="2">
         <v>217430870000</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="2">
         <v>419443904151.30499</v>
       </c>
     </row>
@@ -6343,16 +6344,16 @@
       <c r="B100" s="1">
         <v>44986</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="2">
         <v>140196854408.603</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="2">
         <v>101548282462.46002</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="2">
         <v>224481820000</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="2">
         <v>419972229148.91803</v>
       </c>
     </row>
@@ -6360,16 +6361,16 @@
       <c r="B101" s="1">
         <v>45017</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="2">
         <v>139131937133.53998</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="2">
         <v>101760635609.19002</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="2">
         <v>223445570000</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="2">
         <v>420531802147.98004</v>
       </c>
     </row>
@@ -6377,16 +6378,16 @@
       <c r="B102" s="1">
         <v>45047</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="2">
         <v>134322762592.69699</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="2">
         <v>100588624352.77003</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="2">
         <v>220782340000</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="2">
         <v>414860122797.604</v>
       </c>
     </row>
@@ -6394,16 +6395,16 @@
       <c r="B103" s="1">
         <v>45078</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="2">
         <v>132642637666.19901</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>99386740800.740021</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="2">
         <v>218227680000</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="2">
         <v>415323758063.44501</v>
       </c>
     </row>
@@ -6411,16 +6412,16 @@
       <c r="B104" s="1">
         <v>45108</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="2">
         <v>132735023302.83099</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="2">
         <v>99951448527.360046</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="2">
         <v>220718000000</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="2">
         <v>415718954603.00397</v>
       </c>
     </row>
@@ -6428,16 +6429,16 @@
       <c r="B105" s="1">
         <v>45139</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="2">
         <v>132175978969.73399</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="2">
         <v>99567906587.89006</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="2">
         <v>216932760000</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="2">
         <v>412228735418.612</v>
       </c>
     </row>
@@ -6445,16 +6446,16 @@
       <c r="B106" s="1">
         <v>45170</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="2">
         <v>130147364552.711</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="2">
         <v>98115969455.810013</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="2">
         <v>211750230000</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="2">
         <v>408085359231.58002</v>
       </c>
     </row>
@@ -6462,16 +6463,16 @@
       <c r="B107" s="1">
         <v>45200</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="2">
         <v>128113214985.045</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <v>101035155405.75998</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="2">
         <v>210925400000</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="2">
         <v>406854466374.16602</v>
       </c>
     </row>
@@ -6479,16 +6480,16 @@
       <c r="B108" s="1">
         <v>45231</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="2">
         <v>132914351368.271</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <v>102720139135.29999</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="2">
         <v>219086890000</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="2">
         <v>410959487230.63599</v>
       </c>
     </row>
@@ -6496,16 +6497,16 @@
       <c r="B109" s="1">
         <v>45261</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="2">
         <v>141149364857.112</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <v>103753228918.42</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="2">
         <v>224483890000</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="2">
         <v>414004455885.98486</v>
       </c>
     </row>
@@ -6513,16 +6514,16 @@
       <c r="B110" s="1">
         <v>45292</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="2">
         <v>139905364331.83301</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <v>103269901747.65001</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="2">
         <v>221626590000</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="2">
         <v>409630958191.48999</v>
       </c>
     </row>
@@ -6530,16 +6531,16 @@
       <c r="B111" s="1">
         <v>45323</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="2">
         <v>138899244265.89001</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="2">
         <v>101994498577.84999</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="2">
         <v>222435040000</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="2">
         <v>409633386762.73798</v>
       </c>
     </row>
@@ -6547,16 +6548,16 @@
       <c r="B112" s="1">
         <v>45352</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="2">
         <v>134841953521.14999</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="2">
         <v>104067517621.14003</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="2">
         <v>223363270000</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="2">
         <v>413141851973.17999</v>
       </c>
     </row>
@@ -6564,16 +6565,16 @@
       <c r="B113" s="1">
         <v>45383</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="2">
         <v>130363578520.94099</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="2">
         <v>102647754826.15005</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="2">
         <v>221069820000</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="2">
         <v>407146321632.42999</v>
       </c>
     </row>
@@ -6581,16 +6582,16 @@
       <c r="B114" s="1">
         <v>45413</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="2">
         <v>133070445944.67599</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="2">
         <v>105015612140.25002</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="2">
         <v>224333600000</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="2">
         <v>406727359460.32703</v>
       </c>
     </row>
@@ -6598,16 +6599,16 @@
       <c r="B115" s="1">
         <v>45444</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="2">
         <v>134304194847.571</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <v>105188872222.01001</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="2">
         <v>224328600000</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="2">
         <v>406109321088.68298</v>
       </c>
     </row>
@@ -6615,16 +6616,16 @@
       <c r="B116" s="1">
         <v>45474</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="2">
         <v>139327488130.63199</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="2">
         <v>106737816558.16</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="2">
         <v>230624330000</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="2">
         <v>407440382632.22803</v>
       </c>
     </row>
@@ -6632,16 +6633,16 @@
       <c r="B117" s="1">
         <v>45505</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="2">
         <v>143869760356.09601</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <v>107857557863.88997</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="2">
         <v>235684780000</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="2">
         <v>409770693591.96796</v>
       </c>
     </row>
@@ -6649,16 +6650,16 @@
       <c r="B118" s="1">
         <v>45536</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="2">
         <v>143232254637.96402</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <v>112706919192.09996</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="2">
         <v>243007410000</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="2">
         <v>413851596411.69</v>
       </c>
     </row>
@@ -6666,16 +6667,16 @@
       <c r="B119" s="1">
         <v>45566</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="2">
         <v>144216272327.33701</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="2">
         <v>111083722126.55</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="2">
         <v>238550540000</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="2">
         <v>409616885730.18298</v>
       </c>
     </row>
@@ -6683,16 +6684,16 @@
       <c r="B120" s="1">
         <v>45597</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="2">
         <v>143518270197.24402</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="2">
         <v>108488025411.82001</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="2">
         <v>237500590000</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="2">
         <v>409307057796.42798</v>
       </c>
     </row>
@@ -6700,16 +6701,16 @@
       <c r="B121" s="1">
         <v>45627</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="2">
         <v>149117682033.45898</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>106256486165.76001</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="2">
         <v>237045760000</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="2">
         <v>409457248116.74603</v>
       </c>
     </row>
@@ -6717,16 +6718,16 @@
       <c r="B122" s="1">
         <v>45658</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="2">
         <v>149007279645.77698</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="2">
         <v>103271181730.51001</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="2">
         <v>242083570000</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="2">
         <v>404837981604.33899</v>
       </c>
     </row>
@@ -6734,16 +6735,16 @@
       <c r="B123" s="1">
         <v>45689</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="2">
         <v>147262544889.38901</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="2">
         <v>107395135883.90001</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="2">
         <v>244755710000</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="2">
         <v>402989855493.17999</v>
       </c>
     </row>
@@ -6751,16 +6752,16 @@
       <c r="B124" s="1">
         <v>45717</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="2">
         <v>149435179668.01199</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="2">
         <v>106669671669.01001</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="2">
         <v>245303690000</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="2">
         <v>403524192612.414</v>
       </c>
     </row>
@@ -6768,16 +6769,16 @@
       <c r="B125" s="1">
         <v>45748</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="2">
         <v>144109871764.901</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="2">
         <v>105307766721.36</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="2">
         <v>256789260000</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="2">
         <v>398460828029.46802</v>
       </c>
     </row>
@@ -6785,16 +6786,16 @@
       <c r="B126" s="1">
         <v>45778</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="2">
         <v>144092428137.608</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="2">
         <v>105176466182.73996</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="2">
         <v>257550540000</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="2">
         <v>398428163623.33685</v>
       </c>
     </row>
@@ -6802,16 +6803,16 @@
       <c r="B127" s="1">
         <v>45809</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="2">
         <v>144250582849.68399</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="2">
         <v>105998082514.60997</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="2">
         <v>262404729999.99997</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="2">
         <v>403999602846.66089</v>
       </c>
     </row>
@@ -6819,39 +6820,55 @@
       <c r="B128" s="1">
         <v>45839</v>
       </c>
-      <c r="D128">
+      <c r="C128" s="2"/>
+      <c r="D128" s="2">
         <v>105418246695.17996</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="2">
         <v>261884310000</v>
       </c>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F128" s="2"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B129" s="1">
         <v>45870</v>
       </c>
-      <c r="D129">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2">
         <v>107097922466.51997</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="2">
         <v>267351450000</v>
       </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F129" s="2"/>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B130" s="1">
         <v>45901</v>
       </c>
-      <c r="D130">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2">
         <v>109059467236.48996</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="2">
         <v>273272500000</v>
       </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F130" s="2"/>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B131" s="1">
         <v>45931</v>
       </c>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6887,19 +6904,19 @@
       <c r="B2" s="1">
         <v>42005</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <f>'International reserves'!C2/'International reserves'!C$2</f>
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <f>'International reserves'!D2/'International reserves'!D$2</f>
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <f>'International reserves'!E2/'International reserves'!E$2</f>
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <f>'International reserves'!F2/'International reserves'!F$2</f>
         <v>1</v>
       </c>
@@ -6908,19 +6925,19 @@
       <c r="B3" s="1">
         <v>42036</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <f>'International reserves'!C3/'International reserves'!C$2</f>
         <v>1.0127403680672897</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <f>'International reserves'!D3/'International reserves'!D$2</f>
         <v>1.0014993627272519</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <f>'International reserves'!E3/'International reserves'!E$2</f>
         <v>1.009730734207245</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <f>'International reserves'!F3/'International reserves'!F$2</f>
         <v>1.0004372325646287</v>
       </c>
@@ -6941,19 +6958,19 @@
       <c r="B4" s="1">
         <v>42064</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <f>'International reserves'!C4/'International reserves'!C$2</f>
         <v>0.97752515505911475</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <f>'International reserves'!D4/'International reserves'!D$2</f>
         <v>0.99681006445922027</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <f>'International reserves'!E4/'International reserves'!E$2</f>
         <v>1.0057660702877906</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <f>'International reserves'!F4/'International reserves'!F$2</f>
         <v>1.0015326709239076</v>
       </c>
@@ -6981,19 +6998,19 @@
       <c r="B5" s="1">
         <v>42095</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <f>'International reserves'!C5/'International reserves'!C$2</f>
         <v>0.97104173827091189</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <f>'International reserves'!D5/'International reserves'!D$2</f>
         <v>1.0016617470925058</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <f>'International reserves'!E5/'International reserves'!E$2</f>
         <v>1.0365472268231068</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <f>'International reserves'!F5/'International reserves'!F$2</f>
         <v>1.021668268435505</v>
       </c>
@@ -7021,19 +7038,19 @@
       <c r="B6" s="1">
         <v>42125</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <f>'International reserves'!C6/'International reserves'!C$2</f>
         <v>0.97056961223967009</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <f>'International reserves'!D6/'International reserves'!D$2</f>
         <v>0.99614763134636775</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <f>'International reserves'!E6/'International reserves'!E$2</f>
         <v>1.0199157126090919</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <f>'International reserves'!F6/'International reserves'!F$2</f>
         <v>1.0260768662408313</v>
       </c>
@@ -7061,19 +7078,19 @@
       <c r="B7" s="1">
         <v>42156</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <f>'International reserves'!C7/'International reserves'!C$2</f>
         <v>0.94613356249956604</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <f>'International reserves'!D7/'International reserves'!D$2</f>
         <v>0.99911136081518004</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <f>'International reserves'!E7/'International reserves'!E$2</f>
         <v>1.0312113373689005</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <f>'International reserves'!F7/'International reserves'!F$2</f>
         <v>1.0351759269470058</v>
       </c>
@@ -7101,19 +7118,19 @@
       <c r="B8" s="1">
         <v>42186</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <f>'International reserves'!C8/'International reserves'!C$2</f>
         <v>0.94379242862213808</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <f>'International reserves'!D8/'International reserves'!D$2</f>
         <v>0.99524751273969159</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <f>'International reserves'!E8/'International reserves'!E$2</f>
         <v>1.009786324431627</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <f>'International reserves'!F8/'International reserves'!F$2</f>
         <v>1.0241594414884827</v>
       </c>
@@ -7141,19 +7158,19 @@
       <c r="B9" s="1">
         <v>42217</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <f>'International reserves'!C9/'International reserves'!C$2</f>
         <v>0.92276943043535342</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <f>'International reserves'!D9/'International reserves'!D$2</f>
         <v>0.99429415956556233</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <f>'International reserves'!E9/'International reserves'!E$2</f>
         <v>1.0026707113702147</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <f>'International reserves'!F9/'International reserves'!F$2</f>
         <v>1.0160429112524931</v>
       </c>
@@ -7162,19 +7179,19 @@
       <c r="B10" s="1">
         <v>42248</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <f>'International reserves'!C10/'International reserves'!C$2</f>
         <v>0.89024067127240925</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <f>'International reserves'!D10/'International reserves'!D$2</f>
         <v>0.99794991290926027</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <f>'International reserves'!E10/'International reserves'!E$2</f>
         <v>1.0007104482148428</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <f>'International reserves'!F10/'International reserves'!F$2</f>
         <v>1.016566526363446</v>
       </c>
@@ -7183,19 +7200,19 @@
       <c r="B11" s="1">
         <v>42278</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <f>'International reserves'!C11/'International reserves'!C$2</f>
         <v>0.88087764870614349</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <f>'International reserves'!D11/'International reserves'!D$2</f>
         <v>1.0047305870087497</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <f>'International reserves'!E11/'International reserves'!E$2</f>
         <v>1.0184716535859137</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <f>'International reserves'!F11/'International reserves'!F$2</f>
         <v>1.0207738503901778</v>
       </c>
@@ -7204,19 +7221,19 @@
       <c r="B12" s="1">
         <v>42309</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <f>'International reserves'!C12/'International reserves'!C$2</f>
         <v>0.87860493106795712</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <f>'International reserves'!D12/'International reserves'!D$2</f>
         <v>0.99327518055983288</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <f>'International reserves'!E12/'International reserves'!E$2</f>
         <v>1.0016597285048077</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <f>'International reserves'!F12/'International reserves'!F$2</f>
         <v>1.0175424488107021</v>
       </c>
@@ -7225,19 +7242,19 @@
       <c r="B13" s="1">
         <v>42339</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <f>'International reserves'!C13/'International reserves'!C$2</f>
         <v>0.92978533342203051</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <f>'International reserves'!D13/'International reserves'!D$2</f>
         <v>0.99939142418997451</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <f>'International reserves'!E13/'International reserves'!E$2</f>
         <v>1.0070191665957313</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <f>'International reserves'!F13/'International reserves'!F$2</f>
         <v>1.0161417575117215</v>
       </c>
@@ -7246,19 +7263,19 @@
       <c r="B14" s="1">
         <v>42370</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <f>'International reserves'!C14/'International reserves'!C$2</f>
         <v>0.89436412865967319</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <f>'International reserves'!D14/'International reserves'!D$2</f>
         <v>0.99970810523639431</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <f>'International reserves'!E14/'International reserves'!E$2</f>
         <v>1.0301836903042862</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <f>'International reserves'!F14/'International reserves'!F$2</f>
         <v>1.01426436000902</v>
       </c>
@@ -7267,19 +7284,19 @@
       <c r="B15" s="1">
         <v>42401</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <f>'International reserves'!C15/'International reserves'!C$2</f>
         <v>0.91342818626380251</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <f>'International reserves'!D15/'International reserves'!D$2</f>
         <v>1.0143912398318786</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <f>'International reserves'!E15/'International reserves'!E$2</f>
         <v>1.0807365009852787</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <f>'International reserves'!F15/'International reserves'!F$2</f>
         <v>1.0099253845025029</v>
       </c>
@@ -7288,19 +7305,19 @@
       <c r="B16" s="1">
         <v>42430</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <f>'International reserves'!C16/'International reserves'!C$2</f>
         <v>0.94036962127108359</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <f>'International reserves'!D16/'International reserves'!D$2</f>
         <v>1.0280124879931485</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <f>'International reserves'!E16/'International reserves'!E$2</f>
         <v>1.1264309576812339</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <f>'International reserves'!F16/'International reserves'!F$2</f>
         <v>1.0214256929264305</v>
       </c>
@@ -7309,19 +7326,19 @@
       <c r="B17" s="1">
         <v>42461</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <f>'International reserves'!C17/'International reserves'!C$2</f>
         <v>0.94146460464176318</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <f>'International reserves'!D17/'International reserves'!D$2</f>
         <v>1.0374186835441721</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <f>'International reserves'!E17/'International reserves'!E$2</f>
         <v>1.1489182972328229</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <f>'International reserves'!F17/'International reserves'!F$2</f>
         <v>1.0288302227806387</v>
       </c>
@@ -7330,19 +7347,19 @@
       <c r="B18" s="1">
         <v>42491</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <f>'International reserves'!C18/'International reserves'!C$2</f>
         <v>0.90515677561344055</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <f>'International reserves'!D18/'International reserves'!D$2</f>
         <v>1.02739497376013</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <f>'International reserves'!E18/'International reserves'!E$2</f>
         <v>1.1290284495197975</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <f>'International reserves'!F18/'International reserves'!F$2</f>
         <v>1.0243387391833081</v>
       </c>
@@ -7351,19 +7368,19 @@
       <c r="B19" s="1">
         <v>42522</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <f>'International reserves'!C19/'International reserves'!C$2</f>
         <v>0.95867925271228849</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <f>'International reserves'!D19/'International reserves'!D$2</f>
         <v>1.056597608249271</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <f>'International reserves'!E19/'International reserves'!E$2</f>
         <v>1.149565241337174</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <f>'International reserves'!F19/'International reserves'!F$2</f>
         <v>1.021572761152491</v>
       </c>
@@ -7372,19 +7389,19 @@
       <c r="B20" s="1">
         <v>42552</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <f>'International reserves'!C20/'International reserves'!C$2</f>
         <v>0.97280881419212006</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <f>'International reserves'!D20/'International reserves'!D$2</f>
         <v>1.0593468711652692</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <f>'International reserves'!E20/'International reserves'!E$2</f>
         <v>1.1594400340078346</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <f>'International reserves'!F20/'International reserves'!F$2</f>
         <v>1.0257548414920128</v>
       </c>
@@ -7393,19 +7410,19 @@
       <c r="B21" s="1">
         <v>42583</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <f>'International reserves'!C21/'International reserves'!C$2</f>
         <v>0.99242954647032244</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <f>'International reserves'!D21/'International reserves'!D$2</f>
         <v>1.0628870778215029</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <f>'International reserves'!E21/'International reserves'!E$2</f>
         <v>1.16329390352175</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <f>'International reserves'!F21/'International reserves'!F$2</f>
         <v>1.0371189496650119</v>
       </c>
@@ -7414,19 +7431,19 @@
       <c r="B22" s="1">
         <v>42614</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <f>'International reserves'!C22/'International reserves'!C$2</f>
         <v>1.0116196707419327</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <f>'International reserves'!D22/'International reserves'!D$2</f>
         <v>1.0671877153256004</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <f>'International reserves'!E22/'International reserves'!E$2</f>
         <v>1.1611455729753271</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <f>'International reserves'!F22/'International reserves'!F$2</f>
         <v>1.0435764674959147</v>
       </c>
@@ -7435,19 +7452,19 @@
       <c r="B23" s="1">
         <v>42644</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <f>'International reserves'!C23/'International reserves'!C$2</f>
         <v>1.0070147550676349</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <f>'International reserves'!D23/'International reserves'!D$2</f>
         <v>1.0543856189116487</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <f>'International reserves'!E23/'International reserves'!E$2</f>
         <v>1.159810056438876</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <f>'International reserves'!F23/'International reserves'!F$2</f>
         <v>1.036331927499101</v>
       </c>
@@ -7456,19 +7473,19 @@
       <c r="B24" s="1">
         <v>42675</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <f>'International reserves'!C24/'International reserves'!C$2</f>
         <v>0.97680871105614875</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <f>'International reserves'!D24/'International reserves'!D$2</f>
         <v>1.0091070781073148</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <f>'International reserves'!E24/'International reserves'!E$2</f>
         <v>1.1240629685398578</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <f>'International reserves'!F24/'International reserves'!F$2</f>
         <v>1.0274278291964851</v>
       </c>
@@ -7477,19 +7494,19 @@
       <c r="B25" s="1">
         <v>42705</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <f>'International reserves'!C25/'International reserves'!C$2</f>
         <v>1.0218483908472082</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <f>'International reserves'!D25/'International reserves'!D$2</f>
         <v>0.999700186828686</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <f>'International reserves'!E25/'International reserves'!E$2</f>
         <v>1.1057129829103167</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <f>'International reserves'!F25/'International reserves'!F$2</f>
         <v>1.0249800105920808</v>
       </c>
@@ -7498,19 +7515,19 @@
       <c r="B26" s="1">
         <v>42736</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <f>'International reserves'!C26/'International reserves'!C$2</f>
         <v>1.0255506361767321</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <f>'International reserves'!D26/'International reserves'!D$2</f>
         <v>1.0081825304900482</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <f>'International reserves'!E26/'International reserves'!E$2</f>
         <v>1.1527341414890884</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <f>'International reserves'!F26/'International reserves'!F$2</f>
         <v>1.0331933837910241</v>
       </c>
@@ -7519,19 +7536,19 @@
       <c r="B27" s="1">
         <v>42767</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <f>'International reserves'!C27/'International reserves'!C$2</f>
         <v>1.0508062218102887</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <f>'International reserves'!D27/'International reserves'!D$2</f>
         <v>1.0089214223886331</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <f>'International reserves'!E27/'International reserves'!E$2</f>
         <v>1.1774456047402504</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <f>'International reserves'!F27/'International reserves'!F$2</f>
         <v>1.0328047679699308</v>
       </c>
@@ -7540,19 +7557,19 @@
       <c r="B28" s="1">
         <v>42795</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <f>'International reserves'!C28/'International reserves'!C$2</f>
         <v>1.0684137805749772</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <f>'International reserves'!D28/'International reserves'!D$2</f>
         <v>1.0022028136658407</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <f>'International reserves'!E28/'International reserves'!E$2</f>
         <v>1.1637220897986726</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <f>'International reserves'!F28/'International reserves'!F$2</f>
         <v>1.0366632658900115</v>
       </c>
@@ -7561,19 +7578,19 @@
       <c r="B29" s="1">
         <v>42826</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <f>'International reserves'!C29/'International reserves'!C$2</f>
         <v>1.081182061662775</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <f>'International reserves'!D29/'International reserves'!D$2</f>
         <v>1.0160979002703701</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <f>'International reserves'!E29/'International reserves'!E$2</f>
         <v>1.1868893801503393</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <f>'International reserves'!F29/'International reserves'!F$2</f>
         <v>1.0402671798323049</v>
       </c>
@@ -7582,19 +7599,19 @@
       <c r="B30" s="1">
         <v>42856</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <f>'International reserves'!C30/'International reserves'!C$2</f>
         <v>1.0960972930407789</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <f>'International reserves'!D30/'International reserves'!D$2</f>
         <v>1.0180948075632277</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <f>'International reserves'!E30/'International reserves'!E$2</f>
         <v>1.1848187729731909</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <f>'International reserves'!F30/'International reserves'!F$2</f>
         <v>1.04555317280732</v>
       </c>
@@ -7603,19 +7620,19 @@
       <c r="B31" s="1">
         <v>42887</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <f>'International reserves'!C31/'International reserves'!C$2</f>
         <v>1.079971678999003</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <f>'International reserves'!D31/'International reserves'!D$2</f>
         <v>1.0074981357971422</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <f>'International reserves'!E31/'International reserves'!E$2</f>
         <v>1.1938715509370201</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <f>'International reserves'!F31/'International reserves'!F$2</f>
         <v>1.0514339281909519</v>
       </c>
@@ -7624,19 +7641,19 @@
       <c r="B32" s="1">
         <v>42917</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <f>'International reserves'!C32/'International reserves'!C$2</f>
         <v>1.1208115904964364</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <f>'International reserves'!D32/'International reserves'!D$2</f>
         <v>1.0043271314421844</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <f>'International reserves'!E32/'International reserves'!E$2</f>
         <v>1.2249237741567351</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <f>'International reserves'!F32/'International reserves'!F$2</f>
         <v>1.0603215988863968</v>
       </c>
@@ -7645,19 +7662,19 @@
       <c r="B33" s="1">
         <v>42948</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <f>'International reserves'!C33/'International reserves'!C$2</f>
         <v>1.1289333218371935</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <f>'International reserves'!D33/'International reserves'!D$2</f>
         <v>1.0125055191976351</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="2">
         <f>'International reserves'!E33/'International reserves'!E$2</f>
         <v>1.2669571899295993</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2">
         <f>'International reserves'!F33/'International reserves'!F$2</f>
         <v>1.0632823540182674</v>
       </c>
@@ -7666,19 +7683,19 @@
       <c r="B34" s="1">
         <v>42979</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <f>'International reserves'!C34/'International reserves'!C$2</f>
         <v>1.1351703993240385</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <f>'International reserves'!D34/'International reserves'!D$2</f>
         <v>1.0030507618344093</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <f>'International reserves'!E34/'International reserves'!E$2</f>
         <v>1.2823357365167487</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <f>'International reserves'!F34/'International reserves'!F$2</f>
         <v>1.062884555964122</v>
       </c>
@@ -7687,19 +7704,19 @@
       <c r="B35" s="1">
         <v>43009</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <f>'International reserves'!C35/'International reserves'!C$2</f>
         <v>1.1097206620626323</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <f>'International reserves'!D35/'International reserves'!D$2</f>
         <v>0.99632191676048698</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <f>'International reserves'!E35/'International reserves'!E$2</f>
         <v>1.2901935176779809</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <f>'International reserves'!F35/'International reserves'!F$2</f>
         <v>1.0622897810470548</v>
       </c>
@@ -7708,19 +7725,19 @@
       <c r="B36" s="1">
         <v>43040</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <f>'International reserves'!C36/'International reserves'!C$2</f>
         <v>1.1041845634469931</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <f>'International reserves'!D36/'International reserves'!D$2</f>
         <v>0.99496826582670128</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <f>'International reserves'!E36/'International reserves'!E$2</f>
         <v>1.30658298279</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <f>'International reserves'!F36/'International reserves'!F$2</f>
         <v>1.0700694852874422</v>
       </c>
@@ -7729,19 +7746,19 @@
       <c r="B37" s="1">
         <v>43070</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <f>'International reserves'!C37/'International reserves'!C$2</f>
         <v>1.1421724391415364</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <f>'International reserves'!D37/'International reserves'!D$2</f>
         <v>1.0105792341965243</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <f>'International reserves'!E37/'International reserves'!E$2</f>
         <v>1.3032967898382615</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <f>'International reserves'!F37/'International reserves'!F$2</f>
         <v>1.0757527833016767</v>
       </c>
@@ -7750,19 +7767,19 @@
       <c r="B38" s="1">
         <v>43101</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <f>'International reserves'!C38/'International reserves'!C$2</f>
         <v>1.1569453254760689</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <f>'International reserves'!D38/'International reserves'!D$2</f>
         <v>1.0062938082309667</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="2">
         <f>'International reserves'!E38/'International reserves'!E$2</f>
         <v>1.3811669198788519</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <f>'International reserves'!F38/'International reserves'!F$2</f>
         <v>1.0938162618265486</v>
       </c>
@@ -7771,19 +7788,19 @@
       <c r="B39" s="1">
         <v>43132</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <f>'International reserves'!C39/'International reserves'!C$2</f>
         <v>1.1219620279995255</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <f>'International reserves'!D39/'International reserves'!D$2</f>
         <v>0.99647654991663337</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <f>'International reserves'!E39/'International reserves'!E$2</f>
         <v>1.3687479736751977</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <f>'International reserves'!F39/'International reserves'!F$2</f>
         <v>1.0910712840160959</v>
       </c>
@@ -7792,19 +7809,19 @@
       <c r="B40" s="1">
         <v>43160</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <f>'International reserves'!C40/'International reserves'!C$2</f>
         <v>1.1033290982772375</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <f>'International reserves'!D40/'International reserves'!D$2</f>
         <v>0.99746288550557527</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <f>'International reserves'!E40/'International reserves'!E$2</f>
         <v>1.3872765686367803</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <f>'International reserves'!F40/'International reserves'!F$2</f>
         <v>1.0965948709364155</v>
       </c>
@@ -7813,19 +7830,19 @@
       <c r="B41" s="1">
         <v>43191</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <f>'International reserves'!C41/'International reserves'!C$2</f>
         <v>1.0933772881216237</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <f>'International reserves'!D41/'International reserves'!D$2</f>
         <v>0.98628276592339648</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <f>'International reserves'!E41/'International reserves'!E$2</f>
         <v>1.384300046691928</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <f>'International reserves'!F41/'International reserves'!F$2</f>
         <v>1.1012644647065206</v>
       </c>
@@ -7834,19 +7851,19 @@
       <c r="B42" s="1">
         <v>43221</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <f>'International reserves'!C42/'International reserves'!C$2</f>
         <v>1.0763610746896344</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <f>'International reserves'!D42/'International reserves'!D$2</f>
         <v>0.98124769919602095</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <f>'International reserves'!E42/'International reserves'!E$2</f>
         <v>1.3675798068767295</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2">
         <f>'International reserves'!F42/'International reserves'!F$2</f>
         <v>1.1028526258036302</v>
       </c>
@@ -7855,19 +7872,19 @@
       <c r="B43" s="1">
         <v>43252</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <f>'International reserves'!C43/'International reserves'!C$2</f>
         <v>1.0505560431478995</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <f>'International reserves'!D43/'International reserves'!D$2</f>
         <v>0.9604677869937619</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="2">
         <f>'International reserves'!E43/'International reserves'!E$2</f>
         <v>1.330502542705871</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <f>'International reserves'!F43/'International reserves'!F$2</f>
         <v>1.1064360648970382</v>
       </c>
@@ -7876,19 +7893,19 @@
       <c r="B44" s="1">
         <v>43282</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <f>'International reserves'!C44/'International reserves'!C$2</f>
         <v>1.0374395278590729</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <f>'International reserves'!D44/'International reserves'!D$2</f>
         <v>0.95051368512831047</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="2">
         <f>'International reserves'!E44/'International reserves'!E$2</f>
         <v>1.322241410715183</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <f>'International reserves'!F44/'International reserves'!F$2</f>
         <v>1.1123812437332765</v>
       </c>
@@ -7897,19 +7914,19 @@
       <c r="B45" s="1">
         <v>43313</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
         <f>'International reserves'!C45/'International reserves'!C$2</f>
         <v>1.0345322611509418</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <f>'International reserves'!D45/'International reserves'!D$2</f>
         <v>0.96553283133156775</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="2">
         <f>'International reserves'!E45/'International reserves'!E$2</f>
         <v>1.3159935584827498</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="2">
         <f>'International reserves'!F45/'International reserves'!F$2</f>
         <v>1.1086713381055762</v>
       </c>
@@ -7918,19 +7935,19 @@
       <c r="B46" s="1">
         <v>43344</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2">
         <f>'International reserves'!C46/'International reserves'!C$2</f>
         <v>1.0069734944350732</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <f>'International reserves'!D46/'International reserves'!D$2</f>
         <v>0.92842565672630739</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="2">
         <f>'International reserves'!E46/'International reserves'!E$2</f>
         <v>1.3154877131770901</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="2">
         <f>'International reserves'!F46/'International reserves'!F$2</f>
         <v>1.1138373588396231</v>
       </c>
@@ -7939,19 +7956,19 @@
       <c r="B47" s="1">
         <v>43374</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2">
         <f>'International reserves'!C47/'International reserves'!C$2</f>
         <v>1.0090210684637586</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <f>'International reserves'!D47/'International reserves'!D$2</f>
         <v>0.92560233116155355</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="2">
         <f>'International reserves'!E47/'International reserves'!E$2</f>
         <v>1.2982926401952968</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <f>'International reserves'!F47/'International reserves'!F$2</f>
         <v>1.113209122487604</v>
       </c>
@@ -7960,19 +7977,19 @@
       <c r="B48" s="1">
         <v>43405</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2">
         <f>'International reserves'!C48/'International reserves'!C$2</f>
         <v>1.0274473059128606</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <f>'International reserves'!D48/'International reserves'!D$2</f>
         <v>0.9376351813619318</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <f>'International reserves'!E48/'International reserves'!E$2</f>
         <v>1.3070975140682193</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <f>'International reserves'!F48/'International reserves'!F$2</f>
         <v>1.1138795829950747</v>
       </c>
@@ -7981,19 +7998,19 @@
       <c r="B49" s="1">
         <v>43435</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2">
         <f>'International reserves'!C49/'International reserves'!C$2</f>
         <v>1.057243796209749</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <f>'International reserves'!D49/'International reserves'!D$2</f>
         <v>0.98113611893731179</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="2">
         <f>'International reserves'!E49/'International reserves'!E$2</f>
         <v>1.323105697155138</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <f>'International reserves'!F49/'International reserves'!F$2</f>
         <v>1.1158421928466535</v>
       </c>
@@ -8002,19 +8019,19 @@
       <c r="B50" s="1">
         <v>43466</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2">
         <f>'International reserves'!C50/'International reserves'!C$2</f>
         <v>1.0513693751704494</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="2">
         <f>'International reserves'!D50/'International reserves'!D$2</f>
         <v>1.0219422308550163</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="2">
         <f>'International reserves'!E50/'International reserves'!E$2</f>
         <v>1.3505770477614607</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="2">
         <f>'International reserves'!F50/'International reserves'!F$2</f>
         <v>1.120897669510269</v>
       </c>
@@ -8023,19 +8040,19 @@
       <c r="B51" s="1">
         <v>43497</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="2">
         <f>'International reserves'!C51/'International reserves'!C$2</f>
         <v>1.0798371128310582</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <f>'International reserves'!D51/'International reserves'!D$2</f>
         <v>1.0255816401163766</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="2">
         <f>'International reserves'!E51/'International reserves'!E$2</f>
         <v>1.3674982874157438</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="2">
         <f>'International reserves'!F51/'International reserves'!F$2</f>
         <v>1.1185143137792806</v>
       </c>
@@ -8044,19 +8061,19 @@
       <c r="B52" s="1">
         <v>43525</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="2">
         <f>'International reserves'!C52/'International reserves'!C$2</f>
         <v>1.0918585974875774</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <f>'International reserves'!D52/'International reserves'!D$2</f>
         <v>1.0358943632085655</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="2">
         <f>'International reserves'!E52/'International reserves'!E$2</f>
         <v>1.3651971480928082</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <f>'International reserves'!F52/'International reserves'!F$2</f>
         <v>1.1201357231448266</v>
       </c>
@@ -8065,19 +8082,19 @@
       <c r="B53" s="1">
         <v>43556</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2">
         <f>'International reserves'!C53/'International reserves'!C$2</f>
         <v>1.0897875853041714</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <f>'International reserves'!D53/'International reserves'!D$2</f>
         <v>1.0391841138867857</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="2">
         <f>'International reserves'!E53/'International reserves'!E$2</f>
         <v>1.3543715309592834</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <f>'International reserves'!F53/'International reserves'!F$2</f>
         <v>1.1164184835621074</v>
       </c>
@@ -8086,19 +8103,19 @@
       <c r="B54" s="1">
         <v>43586</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="2">
         <f>'International reserves'!C54/'International reserves'!C$2</f>
         <v>1.0544433491726712</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <f>'International reserves'!D54/'International reserves'!D$2</f>
         <v>1.0575037639811917</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="2">
         <f>'International reserves'!E54/'International reserves'!E$2</f>
         <v>1.3508665158395787</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="2">
         <f>'International reserves'!F54/'International reserves'!F$2</f>
         <v>1.1106355876845944</v>
       </c>
@@ -8107,19 +8124,19 @@
       <c r="B55" s="1">
         <v>43617</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="2">
         <f>'International reserves'!C55/'International reserves'!C$2</f>
         <v>1.0829698170660258</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <f>'International reserves'!D55/'International reserves'!D$2</f>
         <v>1.0522271194765249</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="2">
         <f>'International reserves'!E55/'International reserves'!E$2</f>
         <v>1.3885229091882856</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <f>'International reserves'!F55/'International reserves'!F$2</f>
         <v>1.113704605880347</v>
       </c>
@@ -8128,19 +8145,19 @@
       <c r="B56" s="1">
         <v>43647</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="2">
         <f>'International reserves'!C56/'International reserves'!C$2</f>
         <v>1.1011330842788138</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <f>'International reserves'!D56/'International reserves'!D$2</f>
         <v>1.05525261850517</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="2">
         <f>'International reserves'!E56/'International reserves'!E$2</f>
         <v>1.4049778729674582</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <f>'International reserves'!F56/'International reserves'!F$2</f>
         <v>1.1138043681675427</v>
       </c>
@@ -8149,19 +8166,19 @@
       <c r="B57" s="1">
         <v>43678</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="2">
         <f>'International reserves'!C57/'International reserves'!C$2</f>
         <v>1.1033857394254172</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <f>'International reserves'!D57/'International reserves'!D$2</f>
         <v>1.0658483827453351</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="2">
         <f>'International reserves'!E57/'International reserves'!E$2</f>
         <v>1.4165837477989907</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="2">
         <f>'International reserves'!F57/'International reserves'!F$2</f>
         <v>1.10922148975543</v>
       </c>
@@ -8170,19 +8187,19 @@
       <c r="B58" s="1">
         <v>43709</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="2">
         <f>'International reserves'!C58/'International reserves'!C$2</f>
         <v>1.0855483130565982</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <f>'International reserves'!D58/'International reserves'!D$2</f>
         <v>1.0602826113877275</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="2">
         <f>'International reserves'!E58/'International reserves'!E$2</f>
         <v>1.4189063768614441</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="2">
         <f>'International reserves'!F58/'International reserves'!F$2</f>
         <v>1.1143691397246491</v>
       </c>
@@ -8191,19 +8208,19 @@
       <c r="B59" s="1">
         <v>43739</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="2">
         <f>'International reserves'!C59/'International reserves'!C$2</f>
         <v>1.1066804039800464</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <f>'International reserves'!D59/'International reserves'!D$2</f>
         <v>1.0634083932076397</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="2">
         <f>'International reserves'!E59/'International reserves'!E$2</f>
         <v>1.433396123263859</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <f>'International reserves'!F59/'International reserves'!F$2</f>
         <v>1.1228460343088029</v>
       </c>
@@ -8212,19 +8229,19 @@
       <c r="B60" s="1">
         <v>43770</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="2">
         <f>'International reserves'!C60/'International reserves'!C$2</f>
         <v>1.1070271244347685</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <f>'International reserves'!D60/'International reserves'!D$2</f>
         <v>1.0682837640664182</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="2">
         <f>'International reserves'!E60/'International reserves'!E$2</f>
         <v>1.422159820479606</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <f>'International reserves'!F60/'International reserves'!F$2</f>
         <v>1.1259535939167675</v>
       </c>
@@ -8233,19 +8250,19 @@
       <c r="B61" s="1">
         <v>43800</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="2">
         <f>'International reserves'!C61/'International reserves'!C$2</f>
         <v>1.1285049375061886</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <f>'International reserves'!D61/'International reserves'!D$2</f>
         <v>1.0882545079484911</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="2">
         <f>'International reserves'!E61/'International reserves'!E$2</f>
         <v>1.4433297875263129</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="2">
         <f>'International reserves'!F61/'International reserves'!F$2</f>
         <v>1.1296213874973069</v>
       </c>
@@ -8254,19 +8271,19 @@
       <c r="B62" s="1">
         <v>43831</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="2">
         <f>'International reserves'!C62/'International reserves'!C$2</f>
         <v>1.1500790747230476</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <f>'International reserves'!D62/'International reserves'!D$2</f>
         <v>1.0762248736012685</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="2">
         <f>'International reserves'!E62/'International reserves'!E$2</f>
         <v>1.4818235729703086</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <f>'International reserves'!F62/'International reserves'!F$2</f>
         <v>1.1319783830104162</v>
       </c>
@@ -8275,19 +8292,19 @@
       <c r="B63" s="1">
         <v>43862</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="2">
         <f>'International reserves'!C63/'International reserves'!C$2</f>
         <v>1.1371746675277909</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <f>'International reserves'!D63/'International reserves'!D$2</f>
         <v>1.092558949717557</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="2">
         <f>'International reserves'!E63/'International reserves'!E$2</f>
         <v>1.4763325584802405</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="2">
         <f>'International reserves'!F63/'International reserves'!F$2</f>
         <v>1.1305448960231004</v>
       </c>
@@ -8296,19 +8313,19 @@
       <c r="B64" s="1">
         <v>43891</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="2">
         <f>'International reserves'!C64/'International reserves'!C$2</f>
         <v>1.0522919069150807</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="2">
         <f>'International reserves'!D64/'International reserves'!D$2</f>
         <v>1.1009157054156831</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="2">
         <f>'International reserves'!E64/'International reserves'!E$2</f>
         <v>1.4571117236759217</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="2">
         <f>'International reserves'!F64/'International reserves'!F$2</f>
         <v>1.1053714972348858</v>
       </c>
@@ -8317,19 +8334,19 @@
       <c r="B65" s="1">
         <v>43922</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="2">
         <f>'International reserves'!C65/'International reserves'!C$2</f>
         <v>1.1125128944708964</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="2">
         <f>'International reserves'!D65/'International reserves'!D$2</f>
         <v>1.1267000609509199</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="2">
         <f>'International reserves'!E65/'International reserves'!E$2</f>
         <v>1.5165637957983185</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="2">
         <f>'International reserves'!F65/'International reserves'!F$2</f>
         <v>1.1150880168477266</v>
       </c>
@@ -8338,19 +8355,19 @@
       <c r="B66" s="1">
         <v>43952</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="2">
         <f>'International reserves'!C66/'International reserves'!C$2</f>
         <v>1.1363536852558815</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="2">
         <f>'International reserves'!D66/'International reserves'!D$2</f>
         <v>1.1557574541230342</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="2">
         <f>'International reserves'!E66/'International reserves'!E$2</f>
         <v>1.5264520999818496</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="2">
         <f>'International reserves'!F66/'International reserves'!F$2</f>
         <v>1.1232029039769884</v>
       </c>
@@ -8359,19 +8376,19 @@
       <c r="B67" s="1">
         <v>43983</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="2">
         <f>'International reserves'!C67/'International reserves'!C$2</f>
         <v>1.1455813485165447</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="2">
         <f>'International reserves'!D67/'International reserves'!D$2</f>
         <v>1.1580093868175829</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="2">
         <f>'International reserves'!E67/'International reserves'!E$2</f>
         <v>1.5543580709188427</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="2">
         <f>'International reserves'!F67/'International reserves'!F$2</f>
         <v>1.1326836760336525</v>
       </c>
@@ -8380,19 +8397,19 @@
       <c r="B68" s="1">
         <v>44013</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="2">
         <f>'International reserves'!C68/'International reserves'!C$2</f>
         <v>1.1716239451591894</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <f>'International reserves'!D68/'International reserves'!D$2</f>
         <v>1.221573646954309</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="2">
         <f>'International reserves'!E68/'International reserves'!E$2</f>
         <v>1.6108008074222728</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="2">
         <f>'International reserves'!F68/'International reserves'!F$2</f>
         <v>1.1488968008905327</v>
       </c>
@@ -8401,19 +8418,19 @@
       <c r="B69" s="1">
         <v>44044</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="2">
         <f>'International reserves'!C69/'International reserves'!C$2</f>
         <v>1.1890327908095566</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <f>'International reserves'!D69/'International reserves'!D$2</f>
         <v>1.225964006856044</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="2">
         <f>'International reserves'!E69/'International reserves'!E$2</f>
         <v>1.6375841646613329</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="2">
         <f>'International reserves'!F69/'International reserves'!F$2</f>
         <v>1.1555872642363345</v>
       </c>
@@ -8422,19 +8439,19 @@
       <c r="B70" s="1">
         <v>44075</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="2">
         <f>'International reserves'!C70/'International reserves'!C$2</f>
         <v>1.173768335472551</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <f>'International reserves'!D70/'International reserves'!D$2</f>
         <v>1.2444042825841999</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="2">
         <f>'International reserves'!E70/'International reserves'!E$2</f>
         <v>1.6152892033168063</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="2">
         <f>'International reserves'!F70/'International reserves'!F$2</f>
         <v>1.1600815212149351</v>
       </c>
@@ -8443,19 +8460,19 @@
       <c r="B71" s="1">
         <v>44105</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="2">
         <f>'International reserves'!C71/'International reserves'!C$2</f>
         <v>1.1599181613456029</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <f>'International reserves'!D71/'International reserves'!D$2</f>
         <v>1.2860230272878308</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="2">
         <f>'International reserves'!E71/'International reserves'!E$2</f>
         <v>1.5989357045652377</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="2">
         <f>'International reserves'!F71/'International reserves'!F$2</f>
         <v>1.1767422615859426</v>
       </c>
@@ -8464,19 +8481,19 @@
       <c r="B72" s="1">
         <v>44136</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="2">
         <f>'International reserves'!C72/'International reserves'!C$2</f>
         <v>1.1620523918772125</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <f>'International reserves'!D72/'International reserves'!D$2</f>
         <v>1.2985709625674189</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="2">
         <f>'International reserves'!E72/'International reserves'!E$2</f>
         <v>1.6309924122560746</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="2">
         <f>'International reserves'!F72/'International reserves'!F$2</f>
         <v>1.2043870506541743</v>
       </c>
@@ -8485,19 +8502,19 @@
       <c r="B73" s="1">
         <v>44166</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="2">
         <f>'International reserves'!C73/'International reserves'!C$2</f>
         <v>1.1807225289674255</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <f>'International reserves'!D73/'International reserves'!D$2</f>
         <v>1.3642580473413326</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="2">
         <f>'International reserves'!E73/'International reserves'!E$2</f>
         <v>1.6608504107596422</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="2">
         <f>'International reserves'!F73/'International reserves'!F$2</f>
         <v>1.2231011348517478</v>
       </c>
@@ -8506,19 +8523,19 @@
       <c r="B74" s="1">
         <v>44197</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="2">
         <f>'International reserves'!C74/'International reserves'!C$2</f>
         <v>1.2006520141227019</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="2">
         <f>'International reserves'!D74/'International reserves'!D$2</f>
         <v>1.3463727845681179</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="2">
         <f>'International reserves'!E74/'International reserves'!E$2</f>
         <v>1.6525135499563417</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="2">
         <f>'International reserves'!F74/'International reserves'!F$2</f>
         <v>1.2220981912776581</v>
       </c>
@@ -8527,19 +8544,19 @@
       <c r="B75" s="1">
         <v>44228</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="2">
         <f>'International reserves'!C75/'International reserves'!C$2</f>
         <v>1.2091185783549021</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="2">
         <f>'International reserves'!D75/'International reserves'!D$2</f>
         <v>1.3028546475632379</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="2">
         <f>'International reserves'!E75/'International reserves'!E$2</f>
         <v>1.6337115720510109</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="2">
         <f>'International reserves'!F75/'International reserves'!F$2</f>
         <v>1.2354614279145926</v>
       </c>
@@ -8548,19 +8565,19 @@
       <c r="B76" s="1">
         <v>44256</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="2">
         <f>'International reserves'!C76/'International reserves'!C$2</f>
         <v>1.1961238151544611</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <f>'International reserves'!D76/'International reserves'!D$2</f>
         <v>1.2944620175359467</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="2">
         <f>'International reserves'!E76/'International reserves'!E$2</f>
         <v>1.5797858373737583</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="2">
         <f>'International reserves'!F76/'International reserves'!F$2</f>
         <v>1.2316362914532308</v>
       </c>
@@ -8569,19 +8586,19 @@
       <c r="B77" s="1">
         <v>44287</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="2">
         <f>'International reserves'!C77/'International reserves'!C$2</f>
         <v>1.20947591224252</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <f>'International reserves'!D77/'International reserves'!D$2</f>
         <v>1.3343714365054087</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="2">
         <f>'International reserves'!E77/'International reserves'!E$2</f>
         <v>1.6109069049685758</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="2">
         <f>'International reserves'!F77/'International reserves'!F$2</f>
         <v>1.2488592108209577</v>
       </c>
@@ -8590,19 +8607,19 @@
       <c r="B78" s="1">
         <v>44317</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="2">
         <f>'International reserves'!C78/'International reserves'!C$2</f>
         <v>1.1847439161077049</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <f>'International reserves'!D78/'International reserves'!D$2</f>
         <v>1.3287417809596613</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="2">
         <f>'International reserves'!E78/'International reserves'!E$2</f>
         <v>1.6199939764388813</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="2">
         <f>'International reserves'!F78/'International reserves'!F$2</f>
         <v>1.2604762768104618</v>
       </c>
@@ -8611,19 +8628,19 @@
       <c r="B79" s="1">
         <v>44348</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="2">
         <f>'International reserves'!C79/'International reserves'!C$2</f>
         <v>1.1943650857131503</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="2">
         <f>'International reserves'!D79/'International reserves'!D$2</f>
         <v>1.3103069313610587</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="2">
         <f>'International reserves'!E79/'International reserves'!E$2</f>
         <v>1.5861792922425064</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="2">
         <f>'International reserves'!F79/'International reserves'!F$2</f>
         <v>1.2539329589039498</v>
       </c>
@@ -8632,19 +8649,19 @@
       <c r="B80" s="1">
         <v>44378</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="2">
         <f>'International reserves'!C80/'International reserves'!C$2</f>
         <v>1.1949922603760865</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="2">
         <f>'International reserves'!D80/'International reserves'!D$2</f>
         <v>1.327512301615789</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="2">
         <f>'International reserves'!E80/'International reserves'!E$2</f>
         <v>1.5957656462836487</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="2">
         <f>'International reserves'!F80/'International reserves'!F$2</f>
         <v>1.2667554446339602</v>
       </c>
@@ -8653,19 +8670,19 @@
       <c r="B81" s="1">
         <v>44409</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="2">
         <f>'International reserves'!C81/'International reserves'!C$2</f>
         <v>1.2623908623452751</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="2">
         <f>'International reserves'!D81/'International reserves'!D$2</f>
         <v>1.3375872433005651</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="2">
         <f>'International reserves'!E81/'International reserves'!E$2</f>
         <v>1.6214625492068389</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="2">
         <f>'International reserves'!F81/'International reserves'!F$2</f>
         <v>1.2815077845973264</v>
       </c>
@@ -8674,19 +8691,19 @@
       <c r="B82" s="1">
         <v>44440</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="2">
         <f>'International reserves'!C82/'International reserves'!C$2</f>
         <v>1.2826767061419633</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <f>'International reserves'!D82/'International reserves'!D$2</f>
         <v>1.3206334450833048</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="2">
         <f>'International reserves'!E82/'International reserves'!E$2</f>
         <v>1.574223469227626</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="2">
         <f>'International reserves'!F82/'International reserves'!F$2</f>
         <v>1.2814039539423414</v>
       </c>
@@ -8695,19 +8712,19 @@
       <c r="B83" s="1">
         <v>44470</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="2">
         <f>'International reserves'!C83/'International reserves'!C$2</f>
         <v>1.2690184599887873</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="2">
         <f>'International reserves'!D83/'International reserves'!D$2</f>
         <v>1.3366480561160869</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="2">
         <f>'International reserves'!E83/'International reserves'!E$2</f>
         <v>1.5834195335684207</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="2">
         <f>'International reserves'!F83/'International reserves'!F$2</f>
         <v>1.2962967652857478</v>
       </c>
@@ -8716,19 +8733,19 @@
       <c r="B84" s="1">
         <v>44501</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="2">
         <f>'International reserves'!C84/'International reserves'!C$2</f>
         <v>1.2726268260093943</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="2">
         <f>'International reserves'!D84/'International reserves'!D$2</f>
         <v>1.3346010007906826</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="2">
         <f>'International reserves'!E84/'International reserves'!E$2</f>
         <v>1.5635821877339784</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="2">
         <f>'International reserves'!F84/'International reserves'!F$2</f>
         <v>1.2815365901894027</v>
       </c>
@@ -8737,19 +8754,19 @@
       <c r="B85" s="1">
         <v>44531</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <f>'International reserves'!C85/'International reserves'!C$2</f>
         <v>1.2632963412390701</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <f>'International reserves'!D85/'International reserves'!D$2</f>
         <v>1.3478670009276204</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="2">
         <f>'International reserves'!E85/'International reserves'!E$2</f>
         <v>1.5827563756486249</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="2">
         <f>'International reserves'!F85/'International reserves'!F$2</f>
         <v>1.2792227834847558</v>
       </c>
@@ -8758,19 +8775,19 @@
       <c r="B86" s="1">
         <v>44562</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <f>'International reserves'!C86/'International reserves'!C$2</f>
         <v>1.2319399754146589</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <f>'International reserves'!D86/'International reserves'!D$2</f>
         <v>1.3341665288537872</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="2">
         <f>'International reserves'!E86/'International reserves'!E$2</f>
         <v>1.5620109274682044</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="2">
         <f>'International reserves'!F86/'International reserves'!F$2</f>
         <v>1.2747863436122637</v>
       </c>
@@ -8779,19 +8796,19 @@
       <c r="B87" s="1">
         <v>44593</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="2">
         <f>'International reserves'!C87/'International reserves'!C$2</f>
         <v>1.2299300388285384</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <f>'International reserves'!D87/'International reserves'!D$2</f>
         <v>1.3355618032274148</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="2">
         <f>'International reserves'!E87/'International reserves'!E$2</f>
         <v>1.5766821141863101</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="2">
         <f>'International reserves'!F87/'International reserves'!F$2</f>
         <v>1.2754850234850883</v>
       </c>
@@ -8800,19 +8817,19 @@
       <c r="B88" s="1">
         <v>44621</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="2">
         <f>'International reserves'!C88/'International reserves'!C$2</f>
         <v>1.2088155705285335</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <f>'International reserves'!D88/'International reserves'!D$2</f>
         <v>1.3294628989200021</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="2">
         <f>'International reserves'!E88/'International reserves'!E$2</f>
         <v>1.5598106097674984</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="2">
         <f>'International reserves'!F88/'International reserves'!F$2</f>
         <v>1.2643814404296994</v>
       </c>
@@ -8821,19 +8838,19 @@
       <c r="B89" s="1">
         <v>44652</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="2">
         <f>'International reserves'!C89/'International reserves'!C$2</f>
         <v>1.1782495891078024</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="2">
         <f>'International reserves'!D89/'International reserves'!D$2</f>
         <v>1.3058188212155568</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="2">
         <f>'International reserves'!E89/'International reserves'!E$2</f>
         <v>1.4706606827393189</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="2">
         <f>'International reserves'!F89/'International reserves'!F$2</f>
         <v>1.240864170019611</v>
       </c>
@@ -8842,19 +8859,19 @@
       <c r="B90" s="1">
         <v>44682</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="2">
         <f>'International reserves'!C90/'International reserves'!C$2</f>
         <v>1.1783246101710119</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <f>'International reserves'!D90/'International reserves'!D$2</f>
         <v>1.2840936943784853</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="2">
         <f>'International reserves'!E90/'International reserves'!E$2</f>
         <v>1.4798186574819263</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="2">
         <f>'International reserves'!F90/'International reserves'!F$2</f>
         <v>1.2362544450709749</v>
       </c>
@@ -8863,19 +8880,19 @@
       <c r="B91" s="1">
         <v>44713</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="2">
         <f>'International reserves'!C91/'International reserves'!C$2</f>
         <v>1.1863070101341555</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <f>'International reserves'!D91/'International reserves'!D$2</f>
         <v>1.2494881471807324</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="2">
         <f>'International reserves'!E91/'International reserves'!E$2</f>
         <v>1.4302418927544898</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="2">
         <f>'International reserves'!F91/'International reserves'!F$2</f>
         <v>1.209690035362148</v>
       </c>
@@ -8884,19 +8901,19 @@
       <c r="B92" s="1">
         <v>44743</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <f>'International reserves'!C92/'International reserves'!C$2</f>
         <v>1.1502467847764803</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <f>'International reserves'!D92/'International reserves'!D$2</f>
         <v>1.2369120909447224</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="2">
         <f>'International reserves'!E92/'International reserves'!E$2</f>
         <v>1.4156149723261697</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <f>'International reserves'!F92/'International reserves'!F$2</f>
         <v>1.2110932565517925</v>
       </c>
@@ -8905,19 +8922,19 @@
       <c r="B93" s="1">
         <v>44774</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <f>'International reserves'!C93/'International reserves'!C$2</f>
         <v>1.1509883182872844</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <f>'International reserves'!D93/'International reserves'!D$2</f>
         <v>1.2072187746908134</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="2">
         <f>'International reserves'!E93/'International reserves'!E$2</f>
         <v>1.3834530678565549</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="2">
         <f>'International reserves'!F93/'International reserves'!F$2</f>
         <v>1.2046811450573367</v>
       </c>
@@ -8926,19 +8943,19 @@
       <c r="B94" s="1">
         <v>44805</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="2">
         <f>'International reserves'!C94/'International reserves'!C$2</f>
         <v>1.1396662209312027</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="2">
         <f>'International reserves'!D94/'International reserves'!D$2</f>
         <v>1.1521882334274467</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="2">
         <f>'International reserves'!E94/'International reserves'!E$2</f>
         <v>1.2832369544252167</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="2">
         <f>'International reserves'!F94/'International reserves'!F$2</f>
         <v>1.1499791287351666</v>
       </c>
@@ -8947,19 +8964,19 @@
       <c r="B95" s="1">
         <v>44835</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="2">
         <f>'International reserves'!C95/'International reserves'!C$2</f>
         <v>1.1347972966965139</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="2">
         <f>'International reserves'!D95/'International reserves'!D$2</f>
         <v>1.1649224610313285</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="2">
         <f>'International reserves'!E95/'International reserves'!E$2</f>
         <v>1.2990795249686646</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="2">
         <f>'International reserves'!F95/'International reserves'!F$2</f>
         <v>1.1420002290581019</v>
       </c>
@@ -8968,19 +8985,19 @@
       <c r="B96" s="1">
         <v>44866</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="2">
         <f>'International reserves'!C96/'International reserves'!C$2</f>
         <v>1.1665376312326003</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="2">
         <f>'International reserves'!D96/'International reserves'!D$2</f>
         <v>1.1784925618446316</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="2">
         <f>'International reserves'!E96/'International reserves'!E$2</f>
         <v>1.3556327985154837</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="2">
         <f>'International reserves'!F96/'International reserves'!F$2</f>
         <v>1.1479087933150205</v>
       </c>
@@ -8989,19 +9006,19 @@
       <c r="B97" s="1">
         <v>44896</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="2">
         <f>'International reserves'!C97/'International reserves'!C$2</f>
         <v>1.1942758988179922</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="2">
         <f>'International reserves'!D97/'International reserves'!D$2</f>
         <v>1.1912035689385452</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="2">
         <f>'International reserves'!E97/'International reserves'!E$2</f>
         <v>1.3938254059035402</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="2">
         <f>'International reserves'!F97/'International reserves'!F$2</f>
         <v>1.1676070668864955</v>
       </c>
@@ -9010,19 +9027,19 @@
       <c r="B98" s="1">
         <v>44927</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="2">
         <f>'International reserves'!C98/'International reserves'!C$2</f>
         <v>1.2114085725819572</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="2">
         <f>'International reserves'!D98/'International reserves'!D$2</f>
         <v>1.2471569339998219</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="2">
         <f>'International reserves'!E98/'International reserves'!E$2</f>
         <v>1.4507948340467733</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="2">
         <f>'International reserves'!F98/'International reserves'!F$2</f>
         <v>1.1864844067248641</v>
       </c>
@@ -9031,19 +9048,19 @@
       <c r="B99" s="1">
         <v>44958</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="2">
         <f>'International reserves'!C99/'International reserves'!C$2</f>
         <v>1.2222811829239204</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="2">
         <f>'International reserves'!D99/'International reserves'!D$2</f>
         <v>1.2168114736410449</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="2">
         <f>'International reserves'!E99/'International reserves'!E$2</f>
         <v>1.3989619040320993</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="2">
         <f>'International reserves'!F99/'International reserves'!F$2</f>
         <v>1.173661715179152</v>
       </c>
@@ -9052,19 +9069,19 @@
       <c r="B100" s="1">
         <v>44986</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="2">
         <f>'International reserves'!C100/'International reserves'!C$2</f>
         <v>1.2622755076788996</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="2">
         <f>'International reserves'!D100/'International reserves'!D$2</f>
         <v>1.2580938029338717</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="2">
         <f>'International reserves'!E100/'International reserves'!E$2</f>
         <v>1.4443280953058366</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="2">
         <f>'International reserves'!F100/'International reserves'!F$2</f>
         <v>1.1751400411644233</v>
       </c>
@@ -9073,19 +9090,19 @@
       <c r="B101" s="1">
         <v>45017</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="2">
         <f>'International reserves'!C101/'International reserves'!C$2</f>
         <v>1.2526874252665903</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="2">
         <f>'International reserves'!D101/'International reserves'!D$2</f>
         <v>1.2607246714375637</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="2">
         <f>'International reserves'!E101/'International reserves'!E$2</f>
         <v>1.437660807109578</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="2">
         <f>'International reserves'!F101/'International reserves'!F$2</f>
         <v>1.1767058033541871</v>
       </c>
@@ -9094,19 +9111,19 @@
       <c r="B102" s="1">
         <v>45047</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="2">
         <f>'International reserves'!C102/'International reserves'!C$2</f>
         <v>1.2093875719234721</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="2">
         <f>'International reserves'!D102/'International reserves'!D$2</f>
         <v>1.2462044839669799</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="2">
         <f>'International reserves'!E102/'International reserves'!E$2</f>
         <v>1.420525442146565</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="2">
         <f>'International reserves'!F102/'International reserves'!F$2</f>
         <v>1.1608356647053077</v>
       </c>
@@ -9115,19 +9132,19 @@
       <c r="B103" s="1">
         <v>45078</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="2">
         <f>'International reserves'!C103/'International reserves'!C$2</f>
         <v>1.1942604098091338</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <f>'International reserves'!D103/'International reserves'!D$2</f>
         <v>1.2313142050573775</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="2">
         <f>'International reserves'!E103/'International reserves'!E$2</f>
         <v>1.4040886223989615</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="2">
         <f>'International reserves'!F103/'International reserves'!F$2</f>
         <v>1.1621329799265778</v>
       </c>
@@ -9136,19 +9153,19 @@
       <c r="B104" s="1">
         <v>45108</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="2">
         <f>'International reserves'!C104/'International reserves'!C$2</f>
         <v>1.1950922125401851</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="2">
         <f>'International reserves'!D104/'International reserves'!D$2</f>
         <v>1.2383104365455091</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="2">
         <f>'International reserves'!E104/'International reserves'!E$2</f>
         <v>1.4201114751284254</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="2">
         <f>'International reserves'!F104/'International reserves'!F$2</f>
         <v>1.1632387941817406</v>
       </c>
@@ -9157,19 +9174,19 @@
       <c r="B105" s="1">
         <v>45139</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="2">
         <f>'International reserves'!C105/'International reserves'!C$2</f>
         <v>1.1900588045343368</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="2">
         <f>'International reserves'!D105/'International reserves'!D$2</f>
         <v>1.2335586896374231</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="2">
         <f>'International reserves'!E105/'International reserves'!E$2</f>
         <v>1.3957570375197341</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="2">
         <f>'International reserves'!F105/'International reserves'!F$2</f>
         <v>1.1534726810167559</v>
       </c>
@@ -9178,19 +9195,19 @@
       <c r="B106" s="1">
         <v>45170</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="2">
         <f>'International reserves'!C106/'International reserves'!C$2</f>
         <v>1.1717939846570706</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="2">
         <f>'International reserves'!D106/'International reserves'!D$2</f>
         <v>1.2155704670518293</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="2">
         <f>'International reserves'!E106/'International reserves'!E$2</f>
         <v>1.3624123609496432</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="2">
         <f>'International reserves'!F106/'International reserves'!F$2</f>
         <v>1.1418789447526803</v>
       </c>
@@ -9199,19 +9216,19 @@
       <c r="B107" s="1">
         <v>45200</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="2">
         <f>'International reserves'!C107/'International reserves'!C$2</f>
         <v>1.1534793285326401</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <f>'International reserves'!D107/'International reserves'!D$2</f>
         <v>1.2517366105274845</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="2">
         <f>'International reserves'!E107/'International reserves'!E$2</f>
         <v>1.3571053603967649</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="2">
         <f>'International reserves'!F107/'International reserves'!F$2</f>
         <v>1.1384347372962449</v>
       </c>
@@ -9220,19 +9237,19 @@
       <c r="B108" s="1">
         <v>45231</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="2">
         <f>'International reserves'!C108/'International reserves'!C$2</f>
         <v>1.1967068095709046</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <f>'International reserves'!D108/'International reserves'!D$2</f>
         <v>1.2726120752500154</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="2">
         <f>'International reserves'!E108/'International reserves'!E$2</f>
         <v>1.4096168257196924</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="2">
         <f>'International reserves'!F108/'International reserves'!F$2</f>
         <v>1.1499211500717488</v>
       </c>
@@ -9241,19 +9258,19 @@
       <c r="B109" s="1">
         <v>45261</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="2">
         <f>'International reserves'!C109/'International reserves'!C$2</f>
         <v>1.2708515247017707</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <f>'International reserves'!D109/'International reserves'!D$2</f>
         <v>1.285411147991576</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="2">
         <f>'International reserves'!E109/'International reserves'!E$2</f>
         <v>1.4443414137970947</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="2">
         <f>'International reserves'!F109/'International reserves'!F$2</f>
         <v>1.1584413910368299</v>
       </c>
@@ -9262,19 +9279,19 @@
       <c r="B110" s="1">
         <v>45292</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="2">
         <f>'International reserves'!C110/'International reserves'!C$2</f>
         <v>1.2596510494755377</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <f>'International reserves'!D110/'International reserves'!D$2</f>
         <v>1.2794231499320317</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="2">
         <f>'International reserves'!E110/'International reserves'!E$2</f>
         <v>1.4259573920232274</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="2">
         <f>'International reserves'!F110/'International reserves'!F$2</f>
         <v>1.1462037431543581</v>
       </c>
@@ -9283,19 +9300,19 @@
       <c r="B111" s="1">
         <v>45323</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="2">
         <f>'International reserves'!C111/'International reserves'!C$2</f>
         <v>1.2505923532417211</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="2">
         <f>'International reserves'!D111/'International reserves'!D$2</f>
         <v>1.263622027694826</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="2">
         <f>'International reserves'!E111/'International reserves'!E$2</f>
         <v>1.4311590027757151</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="2">
         <f>'International reserves'!F111/'International reserves'!F$2</f>
         <v>1.1462105386306261</v>
       </c>
@@ -9304,19 +9321,19 @@
       <c r="B112" s="1">
         <v>45352</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="2">
         <f>'International reserves'!C112/'International reserves'!C$2</f>
         <v>1.2140621560684575</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="2">
         <f>'International reserves'!D112/'International reserves'!D$2</f>
         <v>1.2893049082762009</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="2">
         <f>'International reserves'!E112/'International reserves'!E$2</f>
         <v>1.4371312844861259</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="2">
         <f>'International reserves'!F112/'International reserves'!F$2</f>
         <v>1.1560277066852327</v>
       </c>
@@ -9325,19 +9342,19 @@
       <c r="B113" s="1">
         <v>45383</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="2">
         <f>'International reserves'!C113/'International reserves'!C$2</f>
         <v>1.1737406873678129</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="2">
         <f>'International reserves'!D113/'International reserves'!D$2</f>
         <v>1.2717152973965362</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="2">
         <f>'International reserves'!E113/'International reserves'!E$2</f>
         <v>1.4223751039180106</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="2">
         <f>'International reserves'!F113/'International reserves'!F$2</f>
         <v>1.1392513884374535</v>
       </c>
@@ -9346,19 +9363,19 @@
       <c r="B114" s="1">
         <v>45413</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="2">
         <f>'International reserves'!C114/'International reserves'!C$2</f>
         <v>1.1981122217073517</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="2">
         <f>'International reserves'!D114/'International reserves'!D$2</f>
         <v>1.301050964537948</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="2">
         <f>'International reserves'!E114/'International reserves'!E$2</f>
         <v>1.4433744398593233</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="2">
         <f>'International reserves'!F114/'International reserves'!F$2</f>
         <v>1.1380790746747813</v>
       </c>
@@ -9367,19 +9384,19 @@
       <c r="B115" s="1">
         <v>45444</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="2">
         <f>'International reserves'!C115/'International reserves'!C$2</f>
         <v>1.2092203954914171</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <f>'International reserves'!D115/'International reserves'!D$2</f>
         <v>1.3031975043894581</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="2">
         <f>'International reserves'!E115/'International reserves'!E$2</f>
         <v>1.4433422695905838</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="2">
         <f>'International reserves'!F115/'International reserves'!F$2</f>
         <v>1.1363497183338471</v>
       </c>
@@ -9388,19 +9405,19 @@
       <c r="B116" s="1">
         <v>45474</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="2">
         <f>'International reserves'!C116/'International reserves'!C$2</f>
         <v>1.2544480869816672</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="2">
         <f>'International reserves'!D116/'International reserves'!D$2</f>
         <v>1.3223875608152791</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="2">
         <f>'International reserves'!E116/'International reserves'!E$2</f>
         <v>1.4838493347928341</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="2">
         <f>'International reserves'!F116/'International reserves'!F$2</f>
         <v>1.1400742115467526</v>
       </c>
@@ -9409,19 +9426,19 @@
       <c r="B117" s="1">
         <v>45505</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="2">
         <f>'International reserves'!C117/'International reserves'!C$2</f>
         <v>1.295344860333677</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <f>'International reserves'!D117/'International reserves'!D$2</f>
         <v>1.3362601696223138</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="2">
         <f>'International reserves'!E117/'International reserves'!E$2</f>
         <v>1.5164085420813815</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="2">
         <f>'International reserves'!F117/'International reserves'!F$2</f>
         <v>1.1465947420177891</v>
       </c>
@@ -9430,19 +9447,19 @@
       <c r="B118" s="1">
         <v>45536</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="2">
         <f>'International reserves'!C118/'International reserves'!C$2</f>
         <v>1.2896050178999949</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <f>'International reserves'!D118/'International reserves'!D$2</f>
         <v>1.3963394864484111</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="2">
         <f>'International reserves'!E118/'International reserves'!E$2</f>
         <v>1.5635227370773479</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="2">
         <f>'International reserves'!F118/'International reserves'!F$2</f>
         <v>1.1580136692103671</v>
       </c>
@@ -9451,19 +9468,19 @@
       <c r="B119" s="1">
         <v>45566</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="2">
         <f>'International reserves'!C119/'International reserves'!C$2</f>
         <v>1.2984647133165426</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="2">
         <f>'International reserves'!D119/'International reserves'!D$2</f>
         <v>1.3762295040874215</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="2">
         <f>'International reserves'!E119/'International reserves'!E$2</f>
         <v>1.5348469959499562</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="2">
         <f>'International reserves'!F119/'International reserves'!F$2</f>
         <v>1.1461643664727306</v>
       </c>
@@ -9472,19 +9489,19 @@
       <c r="B120" s="1">
         <v>45597</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="2">
         <f>'International reserves'!C120/'International reserves'!C$2</f>
         <v>1.2921801857724637</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="2">
         <f>'International reserves'!D120/'International reserves'!D$2</f>
         <v>1.3440711073926783</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="2">
         <f>'International reserves'!E120/'International reserves'!E$2</f>
         <v>1.5280915612173513</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="2">
         <f>'International reserves'!F120/'International reserves'!F$2</f>
         <v>1.1452974253143484</v>
       </c>
@@ -9493,19 +9510,19 @@
       <c r="B121" s="1">
         <v>45627</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="2">
         <f>'International reserves'!C121/'International reserves'!C$2</f>
         <v>1.3425950146077943</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <f>'International reserves'!D121/'International reserves'!D$2</f>
         <v>1.3164243010815064</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="2">
         <f>'International reserves'!E121/'International reserves'!E$2</f>
         <v>1.5251651605511951</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="2">
         <f>'International reserves'!F121/'International reserves'!F$2</f>
         <v>1.1457176784809893</v>
       </c>
@@ -9514,19 +9531,19 @@
       <c r="B122" s="1">
         <v>45658</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="2">
         <f>'International reserves'!C122/'International reserves'!C$2</f>
         <v>1.3416009963714499</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="2">
         <f>'International reserves'!D122/'International reserves'!D$2</f>
         <v>1.2794390077925979</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="2">
         <f>'International reserves'!E122/'International reserves'!E$2</f>
         <v>1.5575787008628903</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="2">
         <f>'International reserves'!F122/'International reserves'!F$2</f>
         <v>1.1327923356540599</v>
       </c>
@@ -9535,19 +9552,19 @@
       <c r="B123" s="1">
         <v>45689</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="2">
         <f>'International reserves'!C123/'International reserves'!C$2</f>
         <v>1.3258921136031823</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="2">
         <f>'International reserves'!D123/'International reserves'!D$2</f>
         <v>1.3305311684687899</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="2">
         <f>'International reserves'!E123/'International reserves'!E$2</f>
         <v>1.5747713932447969</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="2">
         <f>'International reserves'!F123/'International reserves'!F$2</f>
         <v>1.1276210246872713</v>
       </c>
@@ -9556,19 +9573,19 @@
       <c r="B124" s="1">
         <v>45717</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="2">
         <f>'International reserves'!C124/'International reserves'!C$2</f>
         <v>1.3454536342931849</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="2">
         <f>'International reserves'!D124/'International reserves'!D$2</f>
         <v>1.3215433056426433</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="2">
         <f>'International reserves'!E124/'International reserves'!E$2</f>
         <v>1.5782971260175698</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="2">
         <f>'International reserves'!F124/'International reserves'!F$2</f>
         <v>1.1291161734154738</v>
       </c>
@@ -9577,19 +9594,19 @@
       <c r="B125" s="1">
         <v>45748</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="2">
         <f>'International reserves'!C125/'International reserves'!C$2</f>
         <v>1.2975067258885595</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="2">
         <f>'International reserves'!D125/'International reserves'!D$2</f>
         <v>1.3046705025456844</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="2">
         <f>'International reserves'!E125/'International reserves'!E$2</f>
         <v>1.652195900722808</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="2">
         <f>'International reserves'!F125/'International reserves'!F$2</f>
         <v>1.1149481831259926</v>
       </c>
@@ -9598,19 +9615,19 @@
       <c r="B126" s="1">
         <v>45778</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="2">
         <f>'International reserves'!C126/'International reserves'!C$2</f>
         <v>1.297349670556684</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="2">
         <f>'International reserves'!D126/'International reserves'!D$2</f>
         <v>1.3030438044868489</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="2">
         <f>'International reserves'!E126/'International reserves'!E$2</f>
         <v>1.6570940171600075</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="2">
         <f>'International reserves'!F126/'International reserves'!F$2</f>
         <v>1.1148567836264511</v>
       </c>
@@ -9619,19 +9636,19 @@
       <c r="B127" s="1">
         <v>45809</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="2">
         <f>'International reserves'!C127/'International reserves'!C$2</f>
         <v>1.2987736313175702</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="2">
         <f>'International reserves'!D127/'International reserves'!D$2</f>
         <v>1.3132229073771124</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="2">
         <f>'International reserves'!E127/'International reserves'!E$2</f>
         <v>1.6883261365225135</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="2">
         <f>'International reserves'!F127/'International reserves'!F$2</f>
         <v>1.1304464366173408</v>
       </c>
@@ -9640,33 +9657,46 @@
       <c r="B128" s="1">
         <v>45839</v>
       </c>
-      <c r="E128">
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2">
         <f>'International reserves'!E128/'International reserves'!E$2</f>
         <v>1.6849777262710328</v>
       </c>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F128" s="2"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B129" s="1">
         <v>45870</v>
       </c>
-      <c r="E129">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2">
         <f>'International reserves'!E129/'International reserves'!E$2</f>
         <v>1.7201535988783128</v>
       </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F129" s="2"/>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B130" s="1">
         <v>45901</v>
       </c>
-      <c r="E130">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2">
         <f>'International reserves'!E130/'International reserves'!E$2</f>
         <v>1.7582499528223008</v>
       </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F130" s="2"/>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B131" s="1">
         <v>45931</v>
       </c>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
